--- a/documentation/Chatbot_Manual_Test_Cases.xlsx
+++ b/documentation/Chatbot_Manual_Test_Cases.xlsx
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>MARKDOWN_RAG_RESPONSE</t>
+          <t>MARKDOWN_RAG_RESPONSE or FAST_QA_RESPONSE</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>From documents</t>
+          <t>From documents or Quick answer</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
